--- a/input/mapping/044. OCB_GOLD_TCKH_T24_CUSTOMER_PHAT.xlsx
+++ b/input/mapping/044. OCB_GOLD_TCKH_T24_CUSTOMER_PHAT.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30404"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rafflescomvn.sharepoint.com/sites/OCBDataBricks-02.VngCTableau/Shared Documents/01. KHTC - Phân tích/06. Mapping View Layer 1/01.REVIEWED__OK/MAPPING_GOLD_BATCH_01_20260714/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1188" documentId="13_ncr:1_{41AF731F-2010-41DC-BF12-24D975B98159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5B489F56-5AA0-4FAB-9967-892CDEAE3BF6}"/>
+  <xr:revisionPtr revIDLastSave="1199" documentId="13_ncr:1_{41AF731F-2010-41DC-BF12-24D975B98159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD4F07B8-0C08-4645-A7F8-E8E9817F54B8}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="9" r:id="rId1"/>
@@ -106,63 +106,12 @@
     <t>Code mới</t>
   </si>
   <si>
-    <t xml:space="preserve">USE CATALOG IDENTIFIER(:curated);
+    <t>USE CATALOG IDENTIFIER(:curated);
 USE SCHEMA tckh;
-CREATE TABLE IF NOT EXISTS T24_CUSTOMER (
-    IP_ID                   INT,
-    ID                      DECIMAL(10, 0),
-    DATA_DATE               STRING,
-    T_SHORT_NAME            STRING,
-    T_LANGUAGE              STRING,
-    T_CREATE_DATE           STRING,
-    T_EDUCATION_LEVEL       STRING,
-    T_JOB_TITLE             STRING,
-    T_OCCUPATION            STRING,
-    T_MARITAL_STATUS        STRING,
-    T_LABOUR_NUMBER         DECIMAL(6, 0),
-    T_GENDER                STRING,
-    T_BIRTH_INCORP_DATE     STRING,
-    T_RESIDENCE             STRING,
-    T_NATIONALITY           STRING,
-    T_ADDRESS               STRING,
-    T_TOWN_COUNTRY          STRING,
-    T_PROVINCE_1            STRING,
-    T_PHONE_1               STRING,
-    T_SMS_1                 STRING,
-    T_OFF_PHONE             STRING,
-    T_EMAIL_1               STRING,
-    T_PROVINCE_2            STRING,
-    T_TOWN_COUNTRY_2        STRING,
-    T_SMS_2                 STRING,
-    T_PHONE_2               STRING,
-    T_OFF_PHONE_2           STRING,
-    T_SECTOR                DECIMAL(4, 0),
-    T_INDUSTRY              DECIMAL(4, 0),
-    T_CUST_GROUP            STRING,
-    T_TAX_ID                STRING,
-    T_LEGAL_ID              STRING,
-    T_LEGAL_DOC_NAME        STRING,
-    T_CONTACT_DATE          STRING,
-    T_PROVINCE              DECIMAL(4, 0),
-    T_FAX_1                 STRING,
-    T_EMAIL_2               STRING,
-    T_NET_MONTHLY_IN        DECIMAL(20, 4),
-    T_TOTAL_PROPERTY        STRING,
-    T_TOTAL_INCOME          STRING,
-    T_COMPANY_BOOK          STRING,
-    T_ACCOUNT_OFFICER       DECIMAL(8, 0)
-)
-USING DELTA;
--- STEP 1: Xóa dữ liệu cũ theo ngày
--- -------------------------------------------------------
 DELETE FROM T24_CUSTOMER
 WHERE DATA_DATE = :DATADT;
--- -------------------------------------------------------
--- STEP 2: Nạp dữ liệu mới từ Raw Vault
--- -------------------------------------------------------
 INSERT INTO T24_CUSTOMER
 WITH
--- STS HUB: chỉ giữ key có trạng thái MỚI NHẤT (&lt;= :DATADT) = 'D'
 cust_sts_del AS (
     SELECT customer_hashkey
     FROM IDENTIFIER(:cleaned || '.raw_vault.sts_hub_customer')
@@ -170,7 +119,6 @@
     GROUP BY customer_hashkey
     HAVING max_by(cdc_status, source_event_date) = 'D'
 ),
--- HUB active: hub CUSTOMER đã LOẠI key bị xóa (anti-join cust_sts_del)
 cust_active AS (
     SELECT
         h.customer_hashkey,
@@ -182,7 +130,6 @@
       AND h.source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
       AND h.record_source = 't24__t24_customer'
 ),
--- SAT: sat_customer_other — bản mới nhất &lt;= :DATADT, mỗi customer_hashkey
 cust_other AS (
     SELECT
         customer_hashkey,
@@ -194,7 +141,6 @@
     WHERE source_event_date &lt;= TO_DATE(:DATADT, 'yyyyMMdd')
     GROUP BY customer_hashkey
 ),
--- LINK: COMPANY_BOOK — link_customer_branch (con trỏ mới nhất &lt;= :DATADT) → hub_branch.business_key
 cust_branch_cur AS (
     SELECT
         customer_hashkey,
@@ -211,7 +157,6 @@
     JOIN IDENTIFIER(:cleaned || '.raw_vault.hub_branch') hb
         ON l.branch_hashkey = hb.branch_hashkey
 ),
--- LINK: ACCOUNT_OFFICER — link_customer_dept_acct_officer_nvql (con trỏ mới nhất &lt;= :DATADT) → hub_acct_officer.business_key
 cust_officer_cur AS (
     SELECT
         customer_hashkey,
@@ -232,7 +177,6 @@
     hub.customer_hashkey                                           AS IP_ID,
     hub.business_key                                               AS ID,
     DATE_FORMAT(pit.snapshot_date, 'yyyyMMdd')                     AS DATA_DATE,
-    -- sat_customer_information
     si.short_name                                                  AS T_SHORT_NAME,
     si.language                                                    AS T_LANGUAGE,
     TO_CHAR(TO_DATE(si.create_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8)      AS T_CREATE_DATE,
@@ -245,7 +189,6 @@
     TO_CHAR(TO_DATE(si.birth_incorp_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8) AS T_BIRTH_INCORP_DATE,
     si.residence                                                   AS T_RESIDENCE,
     si.nationality                                                 AS T_NATIONALITY,
-    -- sat_customer_contact
     sc.address                                                     AS T_ADDRESS,
     sc.town_country                                                AS T_TOWN_COUNTRY,
     sc.province_1                                                  AS T_PROVINCE_1,
@@ -258,26 +201,20 @@
     sc.sms_2                                                       AS T_SMS_2,
     sc.phone_2                                                     AS T_PHONE_2,
     sc.off_phone_2                                                 AS T_OFF_PHONE_2,
-    -- sat_customer_classification
     scl.sector                                                     AS T_SECTOR,
     scl.industry                                                   AS T_INDUSTRY,
     scl.cust_group                                                 AS T_CUST_GROUP,
-    -- sat_customer_kyc
     sk.tax_id                                                      AS T_TAX_ID,
     sk.legal_id                                                    AS T_LEGAL_ID,
     sk.legal_doc_name                                              AS T_LEGAL_DOC_NAME,
-    -- sat_customer_other
     TO_CHAR(TO_DATE(so.contact_date, 'yyyyMMdd'), 'yyyyMMdd')::VARCHAR(8)      AS T_CONTACT_DATE,
     so.province                                                    AS T_PROVINCE,
     so.fax_1                                                       AS T_FAX_1,
     so.email_2                                                     AS T_EMAIL_2,
-    -- sat_customer_financial_statement
     sf.net_monthly_in                                              AS T_NET_MONTHLY_IN,
     sf.total_property                                              AS T_TOTAL_PROPERTY,
     sf.total_income                                                AS T_TOTAL_INCOME,
-    -- link_customer_branch → hub_branch.business_key
     cb.company_book                                                AS T_COMPANY_BOOK,
-    -- link_customer_dept_acct_officer_nvql → hub_acct_officer.business_key
     ao.account_officer                                             AS T_ACCOUNT_OFFICER
 FROM IDENTIFIER(:cleaned || '.business_vault.pit_customer') pit
 LEFT JOIN cust_active hub
@@ -302,8 +239,7 @@
 LEFT JOIN cust_branch cb
     ON cb.customer_hashkey = hub.customer_hashkey
 LEFT JOIN cust_officer ao
-    ON ao.customer_hashkey = hub.customer_hashkey;
-</t>
+    ON ao.customer_hashkey = hub.customer_hashkey;</t>
   </si>
   <si>
     <t>V_T24_CRB_FULLLIST
@@ -1169,17 +1105,17 @@
     <xf numFmtId="0" fontId="10" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="8" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="6"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="10" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1187,8 +1123,8 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1536,18 +1472,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="30" customHeight="1">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="33"/>
-      <c r="C1" s="33"/>
-      <c r="D1" s="33"/>
-      <c r="E1" s="33"/>
-      <c r="F1" s="33"/>
-      <c r="G1" s="33"/>
-      <c r="H1" s="33"/>
-      <c r="I1" s="33"/>
-      <c r="J1" s="33"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
     </row>
     <row r="2" spans="1:10" ht="6" customHeight="1"/>
     <row r="3" spans="1:10" ht="7.15" customHeight="1"/>
@@ -1558,12 +1494,12 @@
       <c r="B4" s="35"/>
       <c r="C4" s="35"/>
       <c r="D4" s="35"/>
-      <c r="F4" s="34" t="s">
+      <c r="F4" s="33" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="33"/>
     </row>
     <row r="5" spans="1:10" ht="19.899999999999999" customHeight="1">
       <c r="A5" s="35"/>
@@ -1571,10 +1507,10 @@
       <c r="C5" s="35"/>
       <c r="D5" s="35"/>
       <c r="E5" s="23"/>
-      <c r="F5" s="34"/>
-      <c r="G5" s="34"/>
-      <c r="H5" s="34"/>
-      <c r="I5" s="34"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="33"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="33"/>
       <c r="J5" s="23"/>
     </row>
     <row r="6" spans="1:10" ht="153" customHeight="1">
@@ -1585,10 +1521,10 @@
       <c r="E6" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="34"/>
-      <c r="I6" s="34"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
       <c r="J6" s="24"/>
     </row>
     <row r="7" spans="1:10" ht="15.75" customHeight="1"/>
@@ -1654,7 +1590,7 @@
   <cols>
     <col min="1" max="1" width="15.28515625" style="20" customWidth="1"/>
     <col min="2" max="2" width="22.28515625" style="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.42578125" style="20" customWidth="1"/>
+    <col min="3" max="3" width="227" style="20" customWidth="1"/>
     <col min="4" max="16384" width="9.140625" style="20"/>
   </cols>
   <sheetData>
@@ -2011,7 +1947,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="33.75" customHeight="1">
-      <c r="A1" s="39" t="s">
+      <c r="A1" s="36" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="37"/>
@@ -2145,14 +2081,14 @@
       <c r="F9" s="2"/>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="36" t="s">
+      <c r="A10" s="39" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="36"/>
-      <c r="C10" s="36"/>
-      <c r="D10" s="36"/>
-      <c r="E10" s="36"/>
-      <c r="F10" s="36"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="39"/>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="13" t="s">
@@ -3025,6 +2961,25 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008E8AE0589F554649956EA8CE8E02225C" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="23e0626ad55af2d285935a5020239a5e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="4a97ca34-240f-47b1-9756-8fd1dc41a41d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9bc362e37f6e76609c3b52c5d716a607" ns2:_="">
     <xsd:import namespace="4a97ca34-240f-47b1-9756-8fd1dc41a41d"/>
@@ -3196,27 +3151,8 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="4a97ca34-240f-47b1-9756-8fd1dc41a41d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7B05B35-61E9-4FB1-A934-71EE92BFAB94}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A11D5C9-9E08-40A2-9B29-BD56BFBDD611}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3224,5 +3160,5 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2A11D5C9-9E08-40A2-9B29-BD56BFBDD611}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E7B05B35-61E9-4FB1-A934-71EE92BFAB94}"/>
 </file>